--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/71.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/71.xlsx
@@ -426,13 +426,13 @@
         <v>-3.766001233051423</v>
       </c>
       <c r="E2">
-        <v>-3.299769760350769</v>
+        <v>-4.17560833275227</v>
       </c>
       <c r="F2">
-        <v>-3.493459912828015</v>
+        <v>-3.168647113781495</v>
       </c>
       <c r="G2">
-        <v>-2.496641003339687</v>
+        <v>-3.408052791020408</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.068103463068988</v>
       </c>
       <c r="E3">
-        <v>-2.921071592985327</v>
+        <v>-5.929042525470248</v>
       </c>
       <c r="F3">
-        <v>-3.442443249591802</v>
+        <v>-2.927811716928581</v>
       </c>
       <c r="G3">
-        <v>-2.713818495916214</v>
+        <v>-3.150266900424193</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.591291880410187</v>
       </c>
       <c r="E4">
-        <v>-4.154156951377935</v>
+        <v>-6.753827081909273</v>
       </c>
       <c r="F4">
-        <v>-3.334897138053745</v>
+        <v>-2.742751954040963</v>
       </c>
       <c r="G4">
-        <v>-2.896887690382313</v>
+        <v>-3.090227108329474</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.422250801052827</v>
       </c>
       <c r="E5">
-        <v>-4.726501724259377</v>
+        <v>-6.19275820930693</v>
       </c>
       <c r="F5">
-        <v>-3.344428333390356</v>
+        <v>-2.603448721381782</v>
       </c>
       <c r="G5">
-        <v>-2.198850459490722</v>
+        <v>-2.859724575000042</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.485090155980535</v>
       </c>
       <c r="E6">
-        <v>-5.054073420078219</v>
+        <v>-7.830331394538662</v>
       </c>
       <c r="F6">
-        <v>-3.323265202983634</v>
+        <v>-2.831224077762159</v>
       </c>
       <c r="G6">
-        <v>-2.84767921065532</v>
+        <v>-2.962722119751012</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.722712284019901</v>
       </c>
       <c r="E7">
-        <v>-5.954795957151869</v>
+        <v>-8.705237101294584</v>
       </c>
       <c r="F7">
-        <v>-3.458518547410529</v>
+        <v>-2.833441617299453</v>
       </c>
       <c r="G7">
-        <v>-2.453637313581604</v>
+        <v>-2.386162273433183</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-3.051356573229111</v>
       </c>
       <c r="E8">
-        <v>-6.570550681870838</v>
+        <v>-9.721983670918755</v>
       </c>
       <c r="F8">
-        <v>-3.497449330239898</v>
+        <v>-2.678790393401202</v>
       </c>
       <c r="G8">
-        <v>-2.229700504592621</v>
+        <v>-3.280295148381868</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-3.397016048406364</v>
       </c>
       <c r="E9">
-        <v>-7.659186776366776</v>
+        <v>-10.16829195521871</v>
       </c>
       <c r="F9">
-        <v>-3.418235868979792</v>
+        <v>-3.137805338640464</v>
       </c>
       <c r="G9">
-        <v>-2.003374966308363</v>
+        <v>-3.199577098019528</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-3.685049199232368</v>
       </c>
       <c r="E10">
-        <v>-7.728273175827796</v>
+        <v>-10.3492361911432</v>
       </c>
       <c r="F10">
-        <v>-3.395937046863832</v>
+        <v>-2.84301008916919</v>
       </c>
       <c r="G10">
-        <v>-1.880568687003025</v>
+        <v>-2.134213675991221</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.855838791869497</v>
       </c>
       <c r="E11">
-        <v>-8.216261534894354</v>
+        <v>-11.04061190331626</v>
       </c>
       <c r="F11">
-        <v>-3.480052786413705</v>
+        <v>-3.141202473359345</v>
       </c>
       <c r="G11">
-        <v>-1.580609255703268</v>
+        <v>-2.086895179882469</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.861777284136624</v>
       </c>
       <c r="E12">
-        <v>-8.87274535483831</v>
+        <v>-11.10089494930636</v>
       </c>
       <c r="F12">
-        <v>-3.158880662102489</v>
+        <v>-2.709711691812902</v>
       </c>
       <c r="G12">
-        <v>-0.4171635588200388</v>
+        <v>-1.759248801064117</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.677019159858296</v>
       </c>
       <c r="E13">
-        <v>-10.26083132156546</v>
+        <v>-12.38470374505889</v>
       </c>
       <c r="F13">
-        <v>-3.353225595208087</v>
+        <v>-2.700433976901548</v>
       </c>
       <c r="G13">
-        <v>-0.1885050720070149</v>
+        <v>-1.476509220508325</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-3.301669682821807</v>
       </c>
       <c r="E14">
-        <v>-10.37684176869396</v>
+        <v>-13.373079425025</v>
       </c>
       <c r="F14">
-        <v>-3.683914832610066</v>
+        <v>-2.951467404850327</v>
       </c>
       <c r="G14">
-        <v>0.2907599926301586</v>
+        <v>0.6267997361975702</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.763075948105121</v>
       </c>
       <c r="E15">
-        <v>-11.37411137161114</v>
+        <v>-13.80280896598288</v>
       </c>
       <c r="F15">
-        <v>-3.27815728443159</v>
+        <v>-2.539520295438133</v>
       </c>
       <c r="G15">
-        <v>1.372299836946528</v>
+        <v>-0.3648740120487278</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.114241515971507</v>
       </c>
       <c r="E16">
-        <v>-12.29115452900843</v>
+        <v>-14.81730035555123</v>
       </c>
       <c r="F16">
-        <v>-3.120533049924692</v>
+        <v>-2.773730409803457</v>
       </c>
       <c r="G16">
-        <v>2.237813897453737</v>
+        <v>1.352815943326546</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.425321695771065</v>
       </c>
       <c r="E17">
-        <v>-12.73414797033478</v>
+        <v>-14.58638893742611</v>
       </c>
       <c r="F17">
-        <v>-3.076702473907764</v>
+        <v>-2.186177694671795</v>
       </c>
       <c r="G17">
-        <v>2.786575234719949</v>
+        <v>1.531170022411723</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.7737407791490125</v>
       </c>
       <c r="E18">
-        <v>-13.58214548453712</v>
+        <v>-16.4952177157173</v>
       </c>
       <c r="F18">
-        <v>-2.736810903028085</v>
+        <v>-2.215261674184086</v>
       </c>
       <c r="G18">
-        <v>2.497312585703982</v>
+        <v>1.249749492922828</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.2325248030076789</v>
       </c>
       <c r="E19">
-        <v>-14.32636848837969</v>
+        <v>-16.51005299656643</v>
       </c>
       <c r="F19">
-        <v>-2.537359084884228</v>
+        <v>-1.822495411983714</v>
       </c>
       <c r="G19">
-        <v>3.378589634582762</v>
+        <v>1.923469590837374</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.141452446806769</v>
       </c>
       <c r="E20">
-        <v>-15.3590190587188</v>
+        <v>-17.61986423552223</v>
       </c>
       <c r="F20">
-        <v>-2.021895042981194</v>
+        <v>-1.745477124341027</v>
       </c>
       <c r="G20">
-        <v>3.446310766348142</v>
+        <v>2.346359987861728</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.3165261256181182</v>
       </c>
       <c r="E21">
-        <v>-16.27333154628947</v>
+        <v>-18.48835309460929</v>
       </c>
       <c r="F21">
-        <v>-1.796067178364799</v>
+        <v>-1.318025462250635</v>
       </c>
       <c r="G21">
-        <v>3.629901675042193</v>
+        <v>2.461018994034963</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.2892512529709084</v>
       </c>
       <c r="E22">
-        <v>-16.7644354954733</v>
+        <v>-18.88554102134805</v>
       </c>
       <c r="F22">
-        <v>-1.758615031349427</v>
+        <v>-1.249954370925585</v>
       </c>
       <c r="G22">
-        <v>3.718333877290787</v>
+        <v>1.994478506605317</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.08125608411153752</v>
       </c>
       <c r="E23">
-        <v>-17.62022651344285</v>
+        <v>-19.36820842345559</v>
       </c>
       <c r="F23">
-        <v>-1.449889127265274</v>
+        <v>-0.8765843314617642</v>
       </c>
       <c r="G23">
-        <v>3.441631744404373</v>
+        <v>1.877716237412477</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-0.2650260384139349</v>
       </c>
       <c r="E24">
-        <v>-16.97131883051372</v>
+        <v>-20.3557508642043</v>
       </c>
       <c r="F24">
-        <v>-1.175293616911266</v>
+        <v>-0.932560430338538</v>
       </c>
       <c r="G24">
-        <v>2.987451618589155</v>
+        <v>1.503620886198625</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.6946177679443151</v>
       </c>
       <c r="E25">
-        <v>-18.26125012312462</v>
+        <v>-19.30341048887983</v>
       </c>
       <c r="F25">
-        <v>-0.8517241973363482</v>
+        <v>-0.3212186601332804</v>
       </c>
       <c r="G25">
-        <v>2.344525785009998</v>
+        <v>0.9572318721198909</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-1.14895909964685</v>
       </c>
       <c r="E26">
-        <v>-17.32107099202214</v>
+        <v>-20.21996004261029</v>
       </c>
       <c r="F26">
-        <v>-1.10098906088015</v>
+        <v>-0.3756192042099296</v>
       </c>
       <c r="G26">
-        <v>2.575218629189878</v>
+        <v>0.9724665838203927</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-1.572961438678707</v>
       </c>
       <c r="E27">
-        <v>-18.00069984261929</v>
+        <v>-19.49324864775538</v>
       </c>
       <c r="F27">
-        <v>-0.9465722649568916</v>
+        <v>-0.05776883318393967</v>
       </c>
       <c r="G27">
-        <v>1.927262682960092</v>
+        <v>0.277740105482282</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-1.919617068673883</v>
       </c>
       <c r="E28">
-        <v>-18.03605363919718</v>
+        <v>-20.978434154155</v>
       </c>
       <c r="F28">
-        <v>-0.912881734317633</v>
+        <v>-0.1220360613953337</v>
       </c>
       <c r="G28">
-        <v>1.874635170368158</v>
+        <v>0.5678460284390271</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-2.15504460127294</v>
       </c>
       <c r="E29">
-        <v>-17.91622568848021</v>
+        <v>-20.23993514145813</v>
       </c>
       <c r="F29">
-        <v>-0.7052083697009913</v>
+        <v>-0.2503965606635339</v>
       </c>
       <c r="G29">
-        <v>1.653339744734528</v>
+        <v>-0.2678286032065909</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-2.260254497621333</v>
       </c>
       <c r="E30">
-        <v>-17.99288369648206</v>
+        <v>-20.04497075000589</v>
       </c>
       <c r="F30">
-        <v>-0.8257093190514297</v>
+        <v>-0.009493237683590087</v>
       </c>
       <c r="G30">
-        <v>1.092309920057551</v>
+        <v>-0.2297139335720811</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.229665257334144</v>
       </c>
       <c r="E31">
-        <v>-17.54745393613959</v>
+        <v>-20.38546218216862</v>
       </c>
       <c r="F31">
-        <v>-0.9407099088472796</v>
+        <v>-0.268938736607798</v>
       </c>
       <c r="G31">
-        <v>1.07754770426161</v>
+        <v>0.3752416041211817</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-2.068377890188974</v>
       </c>
       <c r="E32">
-        <v>-17.04312231437935</v>
+        <v>-20.98625935724025</v>
       </c>
       <c r="F32">
-        <v>-0.7541267783059132</v>
+        <v>-0.3981723351185489</v>
       </c>
       <c r="G32">
-        <v>0.6093961370462755</v>
+        <v>-0.8584583275713181</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-1.790510732009553</v>
       </c>
       <c r="E33">
-        <v>-16.98477745526452</v>
+        <v>-19.10514936835002</v>
       </c>
       <c r="F33">
-        <v>-0.9134301135382862</v>
+        <v>0.06272134739026242</v>
       </c>
       <c r="G33">
-        <v>0.102677091621228</v>
+        <v>-0.7414269982106034</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-1.418583283312126</v>
       </c>
       <c r="E34">
-        <v>-17.1852575280581</v>
+        <v>-19.10917065326883</v>
       </c>
       <c r="F34">
-        <v>-0.8219692402277899</v>
+        <v>0.06315789701153775</v>
       </c>
       <c r="G34">
-        <v>0.1420517503345646</v>
+        <v>-1.110213332941273</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-0.9823641398293746</v>
       </c>
       <c r="E35">
-        <v>-16.27152921363442</v>
+        <v>-18.27000366338144</v>
       </c>
       <c r="F35">
-        <v>-0.7557959386225542</v>
+        <v>-0.2265892815070761</v>
       </c>
       <c r="G35">
-        <v>-0.08457237911160355</v>
+        <v>-1.850010670619917</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-0.516036574839605</v>
       </c>
       <c r="E36">
-        <v>-15.9555458828012</v>
+        <v>-18.8800208115327</v>
       </c>
       <c r="F36">
-        <v>-0.655464907162881</v>
+        <v>0.1073413575420578</v>
       </c>
       <c r="G36">
-        <v>0.4627550643331317</v>
+        <v>-1.627228851619858</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-0.05603409780468756</v>
       </c>
       <c r="E37">
-        <v>-15.64768663433775</v>
+        <v>-18.45463407714817</v>
       </c>
       <c r="F37">
-        <v>-0.6185081238543838</v>
+        <v>-0.1671017332098352</v>
       </c>
       <c r="G37">
-        <v>0.1336747916933023</v>
+        <v>-1.722358027071279</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.3638924641990627</v>
       </c>
       <c r="E38">
-        <v>-15.2793767863459</v>
+        <v>-17.36445377301562</v>
       </c>
       <c r="F38">
-        <v>-0.3821980981229632</v>
+        <v>0.06585920311206694</v>
       </c>
       <c r="G38">
-        <v>-0.3390409547112196</v>
+        <v>-1.251647107039578</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.7149243519862117</v>
       </c>
       <c r="E39">
-        <v>-14.46769310521107</v>
+        <v>-17.97511396447596</v>
       </c>
       <c r="F39">
-        <v>-0.6020053884558121</v>
+        <v>0.2452363656164803</v>
       </c>
       <c r="G39">
-        <v>0.8725369812275039</v>
+        <v>-1.10863834659274</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>0.9742271144727648</v>
       </c>
       <c r="E40">
-        <v>-14.49878107927372</v>
+        <v>-16.91276113312054</v>
       </c>
       <c r="F40">
-        <v>-0.4618928408440953</v>
+        <v>0.5429855732461374</v>
       </c>
       <c r="G40">
-        <v>0.8441576959598666</v>
+        <v>-0.9037949658581658</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>1.126076075751268</v>
       </c>
       <c r="E41">
-        <v>-13.89047569429737</v>
+        <v>-16.65270445628205</v>
       </c>
       <c r="F41">
-        <v>-0.3885798405941306</v>
+        <v>0.152226445262749</v>
       </c>
       <c r="G41">
-        <v>0.7891873911744892</v>
+        <v>-0.5308874168488332</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>1.163715110820844</v>
       </c>
       <c r="E42">
-        <v>-14.20583409571753</v>
+        <v>-16.06287977373101</v>
       </c>
       <c r="F42">
-        <v>-0.5091743954610854</v>
+        <v>-0.01587829362436868</v>
       </c>
       <c r="G42">
-        <v>1.176447003284833</v>
+        <v>-1.264808086714511</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.089404523000084</v>
       </c>
       <c r="E43">
-        <v>-13.56014162933385</v>
+        <v>-16.00357034965254</v>
       </c>
       <c r="F43">
-        <v>-0.3194674914437623</v>
+        <v>-0.2928263674023274</v>
       </c>
       <c r="G43">
-        <v>1.58596642245445</v>
+        <v>-0.3626427813883054</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.9131326219294341</v>
       </c>
       <c r="E44">
-        <v>-13.11679949550891</v>
+        <v>-15.56574842564296</v>
       </c>
       <c r="F44">
-        <v>-0.445652697912211</v>
+        <v>0.03155816569694501</v>
       </c>
       <c r="G44">
-        <v>1.290577732786998</v>
+        <v>-0.1873074261378176</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.6519324832865243</v>
       </c>
       <c r="E45">
-        <v>-12.2097778510906</v>
+        <v>-15.01085639158708</v>
       </c>
       <c r="F45">
-        <v>-0.4740806104414844</v>
+        <v>0.0001912056225389336</v>
       </c>
       <c r="G45">
-        <v>1.528102080253642</v>
+        <v>0.5446970103371446</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>0.3282627534425756</v>
       </c>
       <c r="E46">
-        <v>-12.74193241715396</v>
+        <v>-14.18690507436547</v>
       </c>
       <c r="F46">
-        <v>-0.2430572254747303</v>
+        <v>0.01760514516419014</v>
       </c>
       <c r="G46">
-        <v>1.998835968836259</v>
+        <v>1.038241951201021</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.03298233994667517</v>
       </c>
       <c r="E47">
-        <v>-12.16736869200876</v>
+        <v>-13.40936155877446</v>
       </c>
       <c r="F47">
-        <v>-0.1870305961863857</v>
+        <v>0.4280943279474572</v>
       </c>
       <c r="G47">
-        <v>2.130114362208083</v>
+        <v>0.1122516961316877</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.4081563335153974</v>
       </c>
       <c r="E48">
-        <v>-10.70127523202549</v>
+        <v>-14.13815152319889</v>
       </c>
       <c r="F48">
-        <v>-0.4908467666741464</v>
+        <v>-0.3374488626563312</v>
       </c>
       <c r="G48">
-        <v>1.53939932608281</v>
+        <v>0.5344858488441526</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.7780996068415194</v>
       </c>
       <c r="E49">
-        <v>-11.76178044598578</v>
+        <v>-13.09012678360374</v>
       </c>
       <c r="F49">
-        <v>-0.3894968433090297</v>
+        <v>0.4386427584547061</v>
       </c>
       <c r="G49">
-        <v>2.159294265536225</v>
+        <v>2.08740926361191</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.128442593743768</v>
       </c>
       <c r="E50">
-        <v>-11.06337654215281</v>
+        <v>-12.09900231991496</v>
       </c>
       <c r="F50">
-        <v>-0.4440208141286959</v>
+        <v>-0.03039874582804121</v>
       </c>
       <c r="G50">
-        <v>1.833514901785197</v>
+        <v>0.7177945724840911</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.449945474596049</v>
       </c>
       <c r="E51">
-        <v>-10.16575600977442</v>
+        <v>-13.05799273204531</v>
       </c>
       <c r="F51">
-        <v>-0.2158818044584897</v>
+        <v>0.3411555122888434</v>
       </c>
       <c r="G51">
-        <v>1.857169228007234</v>
+        <v>1.200724761603164</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.7361695162442</v>
       </c>
       <c r="E52">
-        <v>-9.568328019364492</v>
+        <v>-12.70586312168287</v>
       </c>
       <c r="F52">
-        <v>-0.1731082252475344</v>
+        <v>-0.1367578068778865</v>
       </c>
       <c r="G52">
-        <v>2.532821965420292</v>
+        <v>0.4627714704409289</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.98663348949258</v>
       </c>
       <c r="E53">
-        <v>-9.11704747060411</v>
+        <v>-12.10920044338024</v>
       </c>
       <c r="F53">
-        <v>-0.5275310171071225</v>
+        <v>-0.07571458459818817</v>
       </c>
       <c r="G53">
-        <v>1.637150197560228</v>
+        <v>-0.02475899130448583</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.204910786062331</v>
       </c>
       <c r="E54">
-        <v>-8.461061782800998</v>
+        <v>-10.79168621558862</v>
       </c>
       <c r="F54">
-        <v>-0.2877393631817356</v>
+        <v>0.2112973247563817</v>
       </c>
       <c r="G54">
-        <v>1.290676169433782</v>
+        <v>0.1418515958194385</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.396622225682802</v>
       </c>
       <c r="E55">
-        <v>-9.06155102164011</v>
+        <v>-11.67215288842596</v>
       </c>
       <c r="F55">
-        <v>-0.06765539813635177</v>
+        <v>-0.05650722962947603</v>
       </c>
       <c r="G55">
-        <v>1.280730786887105</v>
+        <v>-0.3655827559055679</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.566022378609546</v>
       </c>
       <c r="E56">
-        <v>-7.746065550203933</v>
+        <v>-10.24910257388559</v>
       </c>
       <c r="F56">
-        <v>-0.2411519804482914</v>
+        <v>0.4849021076966417</v>
       </c>
       <c r="G56">
-        <v>1.129594440637522</v>
+        <v>0.05826903903570326</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.718574465504689</v>
       </c>
       <c r="E57">
-        <v>-7.823543212001165</v>
+        <v>-10.06353476599928</v>
       </c>
       <c r="F57">
-        <v>0.1354221841295582</v>
+        <v>0.1361528041788274</v>
       </c>
       <c r="G57">
-        <v>0.5295049545169156</v>
+        <v>-0.03788387754226469</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.858086966627238</v>
       </c>
       <c r="E58">
-        <v>-6.85248441664038</v>
+        <v>-9.638048405186584</v>
       </c>
       <c r="F58">
-        <v>0.2567572994546158</v>
+        <v>0.04441028595137934</v>
       </c>
       <c r="G58">
-        <v>0.08921095834126692</v>
+        <v>-0.6484863975393318</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.986345160771121</v>
       </c>
       <c r="E59">
-        <v>-6.850351505382767</v>
+        <v>-10.04131354404364</v>
       </c>
       <c r="F59">
-        <v>0.1724228709104037</v>
+        <v>0.9116057540223061</v>
       </c>
       <c r="G59">
-        <v>0.5007680160992988</v>
+        <v>-1.812834430351408</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.101830434369402</v>
       </c>
       <c r="E60">
-        <v>-7.552437058583964</v>
+        <v>-8.3273404738285</v>
       </c>
       <c r="F60">
-        <v>0.1034505158511085</v>
+        <v>0.5123724275082788</v>
       </c>
       <c r="G60">
-        <v>0.2502795622512891</v>
+        <v>-0.8595050372487809</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.202850603894713</v>
       </c>
       <c r="E61">
-        <v>-6.401172168561944</v>
+        <v>-7.813766236618604</v>
       </c>
       <c r="F61">
-        <v>0.5422359007466039</v>
+        <v>0.623467264999929</v>
       </c>
       <c r="G61">
-        <v>-0.151673360002248</v>
+        <v>-1.017558198545673</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.286702472778003</v>
       </c>
       <c r="E62">
-        <v>-6.26557607135027</v>
+        <v>-8.137144565506345</v>
       </c>
       <c r="F62">
-        <v>0.437085427737443</v>
+        <v>0.4553534140713805</v>
       </c>
       <c r="G62">
-        <v>-1.115414069112993</v>
+        <v>-1.572773698619314</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.349648661398419</v>
       </c>
       <c r="E63">
-        <v>-5.975889589079597</v>
+        <v>-7.663837519172654</v>
       </c>
       <c r="F63">
-        <v>0.2124007101369107</v>
+        <v>0.7356472637892464</v>
       </c>
       <c r="G63">
-        <v>-1.129159106225507</v>
+        <v>-1.927782184021875</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.387468761006979</v>
       </c>
       <c r="E64">
-        <v>-6.074125775727991</v>
+        <v>-8.090252217156918</v>
       </c>
       <c r="F64">
-        <v>0.1867279475893484</v>
+        <v>0.2485887684956099</v>
       </c>
       <c r="G64">
-        <v>-1.233547888917681</v>
+        <v>-3.237826297737975</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.398741691471831</v>
       </c>
       <c r="E65">
-        <v>-5.605935905022967</v>
+        <v>-7.454463523428015</v>
       </c>
       <c r="F65">
-        <v>0.3242038017579544</v>
+        <v>0.7647958559589554</v>
       </c>
       <c r="G65">
-        <v>-1.155330129383638</v>
+        <v>-2.521785004149712</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.386805369311706</v>
       </c>
       <c r="E66">
-        <v>-4.919432830882164</v>
+        <v>-8.397260112506929</v>
       </c>
       <c r="F66">
-        <v>-0.03127515854020309</v>
+        <v>0.7292191327435222</v>
       </c>
       <c r="G66">
-        <v>-1.488761301811291</v>
+        <v>-2.497878023867598</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.359779699166301</v>
       </c>
       <c r="E67">
-        <v>-5.100173285476304</v>
+        <v>-7.560583783323763</v>
       </c>
       <c r="F67">
-        <v>0.1281366928219366</v>
+        <v>0.6355133837714394</v>
       </c>
       <c r="G67">
-        <v>-1.454223163676576</v>
+        <v>-3.263990758452988</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.328050278795387</v>
       </c>
       <c r="E68">
-        <v>-4.72103132765811</v>
+        <v>-7.598536923982047</v>
       </c>
       <c r="F68">
-        <v>0.03314034743629207</v>
+        <v>0.4592740769888305</v>
       </c>
       <c r="G68">
-        <v>-1.835435484452863</v>
+        <v>-3.109898031578345</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.300499093333526</v>
       </c>
       <c r="E69">
-        <v>-4.881452519379833</v>
+        <v>-7.341976229077483</v>
       </c>
       <c r="F69">
-        <v>0.0553662732208056</v>
+        <v>0.5599803588819721</v>
       </c>
       <c r="G69">
-        <v>-2.425622243907065</v>
+        <v>-3.560058660983244</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.285555125550139</v>
       </c>
       <c r="E70">
-        <v>-5.043549246484393</v>
+        <v>-7.272038476503022</v>
       </c>
       <c r="F70">
-        <v>-0.18054282268766</v>
+        <v>0.3489222850574916</v>
       </c>
       <c r="G70">
-        <v>-2.013402379394026</v>
+        <v>-3.080288288225915</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.291305213960289</v>
       </c>
       <c r="E71">
-        <v>-4.943089579098235</v>
+        <v>-6.984195083153471</v>
       </c>
       <c r="F71">
-        <v>0.03473246958447272</v>
+        <v>0.1703113624006678</v>
       </c>
       <c r="G71">
-        <v>-2.179146724026257</v>
+        <v>-3.334307336471888</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.325760427489378</v>
       </c>
       <c r="E72">
-        <v>-5.18077106586482</v>
+        <v>-7.452896671421361</v>
       </c>
       <c r="F72">
-        <v>-0.1198251487972618</v>
+        <v>0.9753453121981169</v>
       </c>
       <c r="G72">
-        <v>-2.451563581556035</v>
+        <v>-3.560291627713964</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.397197099978662</v>
       </c>
       <c r="E73">
-        <v>-5.020336288721075</v>
+        <v>-7.578688622406428</v>
       </c>
       <c r="F73">
-        <v>-0.3797784369393859</v>
+        <v>0.320197816998016</v>
       </c>
       <c r="G73">
-        <v>-1.703287567367787</v>
+        <v>-3.927739224048381</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.512877382055972</v>
       </c>
       <c r="E74">
-        <v>-5.143537952573755</v>
+        <v>-8.234112779432589</v>
       </c>
       <c r="F74">
-        <v>-0.1468531204158041</v>
+        <v>-0.09630862659918667</v>
       </c>
       <c r="G74">
-        <v>-2.011883173812003</v>
+        <v>-3.702867266914956</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.672289371477399</v>
       </c>
       <c r="E75">
-        <v>-5.98686661007419</v>
+        <v>-7.322635116590724</v>
       </c>
       <c r="F75">
-        <v>-0.5094800630327185</v>
+        <v>-0.1693209294819351</v>
       </c>
       <c r="G75">
-        <v>-1.670324415581605</v>
+        <v>-2.786310523829026</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.868986294935638</v>
       </c>
       <c r="E76">
-        <v>-5.98301740716767</v>
+        <v>-8.165791692078868</v>
       </c>
       <c r="F76">
-        <v>-0.5348446729064393</v>
+        <v>0.001527362243254536</v>
       </c>
       <c r="G76">
-        <v>-1.640993576061729</v>
+        <v>-3.197916799910449</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.095741252330271</v>
       </c>
       <c r="E77">
-        <v>-6.379231711994781</v>
+        <v>-8.336238925253571</v>
       </c>
       <c r="F77">
-        <v>-0.6756373101558545</v>
+        <v>-0.4214527726068262</v>
       </c>
       <c r="G77">
-        <v>-1.631586313850801</v>
+        <v>-3.112437697065355</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.347745856617887</v>
       </c>
       <c r="E78">
-        <v>-7.119668911566938</v>
+        <v>-9.660016032597794</v>
       </c>
       <c r="F78">
-        <v>-0.6681107639340182</v>
+        <v>-0.496818467280928</v>
       </c>
       <c r="G78">
-        <v>-1.501571190779363</v>
+        <v>-2.677692246546727</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.617612404706243</v>
       </c>
       <c r="E79">
-        <v>-6.913609758795913</v>
+        <v>-8.923799370800785</v>
       </c>
       <c r="F79">
-        <v>-0.6215300081397964</v>
+        <v>-0.5957247068077862</v>
       </c>
       <c r="G79">
-        <v>-1.373856204021097</v>
+        <v>-2.713624903844206</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.895689679013165</v>
       </c>
       <c r="E80">
-        <v>-7.659399614645137</v>
+        <v>-10.33096832699626</v>
       </c>
       <c r="F80">
-        <v>-0.8579725726556648</v>
+        <v>-0.1241633088857228</v>
       </c>
       <c r="G80">
-        <v>-1.002415361048836</v>
+        <v>-2.426865826878095</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-5.17121940365242</v>
       </c>
       <c r="E81">
-        <v>-7.402164177113431</v>
+        <v>-10.47460246557154</v>
       </c>
       <c r="F81">
-        <v>-0.8239308142376193</v>
+        <v>-0.4694119317593064</v>
       </c>
       <c r="G81">
-        <v>-1.126888500906371</v>
+        <v>-2.049909250464408</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-5.435674837402939</v>
       </c>
       <c r="E82">
-        <v>-8.66321739097741</v>
+        <v>-11.77557870628715</v>
       </c>
       <c r="F82">
-        <v>-0.9178163189361096</v>
+        <v>-0.5390511225778553</v>
       </c>
       <c r="G82">
-        <v>-0.9080080543404927</v>
+        <v>-2.306057811502459</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.681301389578349</v>
       </c>
       <c r="E83">
-        <v>-9.881263687190545</v>
+        <v>-12.65988099660898</v>
       </c>
       <c r="F83">
-        <v>-0.9715947590932563</v>
+        <v>-0.59133767304256</v>
       </c>
       <c r="G83">
-        <v>-0.8891246242658885</v>
+        <v>-2.440571489331896</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.900525327930383</v>
       </c>
       <c r="E84">
-        <v>-10.98755630184239</v>
+        <v>-13.18668743486929</v>
       </c>
       <c r="F84">
-        <v>-1.223322358925581</v>
+        <v>-0.6989674496882998</v>
       </c>
       <c r="G84">
-        <v>-1.011304190253372</v>
+        <v>-2.642432239668934</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-6.086327190818832</v>
       </c>
       <c r="E85">
-        <v>-12.16483274656447</v>
+        <v>-13.56286777068647</v>
       </c>
       <c r="F85">
-        <v>-1.451573198195165</v>
+        <v>-0.8525417959629114</v>
       </c>
       <c r="G85">
-        <v>-0.9578038727266257</v>
+        <v>-3.430653845121863</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-6.235447858179327</v>
       </c>
       <c r="E86">
-        <v>-12.82995236644105</v>
+        <v>-16.71279730636384</v>
       </c>
       <c r="F86">
-        <v>-1.465632249755479</v>
+        <v>-1.082913255783662</v>
       </c>
       <c r="G86">
-        <v>-0.3936404814603797</v>
+        <v>-2.298110692885484</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-6.347893298205235</v>
       </c>
       <c r="E87">
-        <v>-13.95536419835328</v>
+        <v>-16.7236973433003</v>
       </c>
       <c r="F87">
-        <v>-1.583219830950271</v>
+        <v>-1.007985767465641</v>
       </c>
       <c r="G87">
-        <v>-0.2494045441503089</v>
+        <v>-1.528017836548488</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-6.425062464811882</v>
       </c>
       <c r="E88">
-        <v>-16.16528215646645</v>
+        <v>-17.81640000745513</v>
       </c>
       <c r="F88">
-        <v>-1.931943455078599</v>
+        <v>-1.196155221583369</v>
       </c>
       <c r="G88">
-        <v>0.07281141298716223</v>
+        <v>-1.31078456320545</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-6.470270410388301</v>
       </c>
       <c r="E89">
-        <v>-17.09708361065475</v>
+        <v>-18.75766144384544</v>
       </c>
       <c r="F89">
-        <v>-2.162362960208712</v>
+        <v>-1.2127051739239</v>
       </c>
       <c r="G89">
-        <v>0.1298521685765492</v>
+        <v>-1.455686588492089</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-6.491831082388347</v>
       </c>
       <c r="E90">
-        <v>-18.41448462659617</v>
+        <v>-21.77792718326119</v>
       </c>
       <c r="F90">
-        <v>-2.11080205958886</v>
+        <v>-1.353742179557141</v>
       </c>
       <c r="G90">
-        <v>-0.4565152489824593</v>
+        <v>-1.698841512154739</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-6.504160149111675</v>
       </c>
       <c r="E91">
-        <v>-20.02108757808944</v>
+        <v>-22.00516148049208</v>
       </c>
       <c r="F91">
-        <v>-2.504861403305001</v>
+        <v>-1.788913397474222</v>
       </c>
       <c r="G91">
-        <v>0.002698270704947553</v>
+        <v>-1.949608869835302</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-6.522050126285955</v>
       </c>
       <c r="E92">
-        <v>-22.9038009195222</v>
+        <v>-24.63407649616495</v>
       </c>
       <c r="F92">
-        <v>-2.697103111574891</v>
+        <v>-1.974181080579943</v>
       </c>
       <c r="G92">
-        <v>0.3467868507576771</v>
+        <v>-1.694369207169216</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-6.558150334712033</v>
       </c>
       <c r="E93">
-        <v>-24.7105624221545</v>
+        <v>-25.78238429265996</v>
       </c>
       <c r="F93">
-        <v>-2.875260917262383</v>
+        <v>-2.192630676739603</v>
       </c>
       <c r="G93">
-        <v>0.2518972044800954</v>
+        <v>-1.834352681338246</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-6.625404460082504</v>
       </c>
       <c r="E94">
-        <v>-26.76983616392851</v>
+        <v>-28.16896255028636</v>
       </c>
       <c r="F94">
-        <v>-2.987319146043489</v>
+        <v>-2.69309049987573</v>
       </c>
       <c r="G94">
-        <v>0.3677079194206966</v>
+        <v>-1.969319167742886</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-6.737843163311564</v>
       </c>
       <c r="E95">
-        <v>-28.94462674916419</v>
+        <v>-30.98705909610367</v>
       </c>
       <c r="F95">
-        <v>-2.940223974092129</v>
+        <v>-2.362675452084077</v>
       </c>
       <c r="G95">
-        <v>0.0001815737688534555</v>
+        <v>-2.114106350274944</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.90856064433033</v>
       </c>
       <c r="E96">
-        <v>-32.03733901575464</v>
+        <v>-33.51550991591638</v>
       </c>
       <c r="F96">
-        <v>-3.376135752467313</v>
+        <v>-2.977279333121559</v>
       </c>
       <c r="G96">
-        <v>-0.8324218344971243</v>
+        <v>-1.593947421342411</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.13608541019577</v>
       </c>
       <c r="E97">
-        <v>-34.27410176778528</v>
+        <v>-36.4966179405878</v>
       </c>
       <c r="F97">
-        <v>-3.801134618678016</v>
+        <v>-3.061417438591308</v>
       </c>
       <c r="G97">
-        <v>-0.3174341107422761</v>
+        <v>-1.72655142822425</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.428427352745799</v>
       </c>
       <c r="E98">
-        <v>-36.99666789017378</v>
+        <v>-38.13503568622196</v>
       </c>
       <c r="F98">
-        <v>-3.621881711284022</v>
+        <v>-3.453075345206734</v>
       </c>
       <c r="G98">
-        <v>-0.9337098628156232</v>
+        <v>-2.949383954111869</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-7.76834355510842</v>
       </c>
       <c r="E99">
-        <v>-39.37444958704029</v>
+        <v>-40.67436390060109</v>
       </c>
       <c r="F99">
-        <v>-4.01404906385217</v>
+        <v>-3.185829110450363</v>
       </c>
       <c r="G99">
-        <v>-0.9994491367590981</v>
+        <v>-1.994712541391429</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-8.171139945131083</v>
       </c>
       <c r="E100">
-        <v>-42.0458371604311</v>
+        <v>-43.53044981486875</v>
       </c>
       <c r="F100">
-        <v>-4.451701242140635</v>
+        <v>-3.739589405752221</v>
       </c>
       <c r="G100">
-        <v>-1.594918662924006</v>
+        <v>-2.89099461646155</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-8.586962972434877</v>
       </c>
       <c r="E101">
-        <v>-44.60797982686087</v>
+        <v>-45.45444898108563</v>
       </c>
       <c r="F101">
-        <v>-4.308930463533335</v>
+        <v>-3.883742729554794</v>
       </c>
       <c r="G101">
-        <v>-1.838214679113713</v>
+        <v>-2.934562676327857</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-9.062995523516165</v>
       </c>
       <c r="E102">
-        <v>-48.00126502723644</v>
+        <v>-48.06560332170042</v>
       </c>
       <c r="F102">
-        <v>-4.732926176819248</v>
+        <v>-3.84557073126639</v>
       </c>
       <c r="G102">
-        <v>-1.709984540570614</v>
+        <v>-3.094450040476479</v>
       </c>
     </row>
   </sheetData>
